--- a/Paper/Survey.xlsx
+++ b/Paper/Survey.xlsx
@@ -1,17 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rubaa\Desktop\Master\Explainable-Deep-Learning-and-Large-Language-Models-for-Forecasting-Cryptocurrency-Prices\Paper\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B82660E-694B-40C7-90CC-EEEB17C76DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="332">
   <si>
     <t>Paper information</t>
   </si>
@@ -28,9 +38,6 @@
     <t>Relevance to my thesis</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>Explainable Artificial Intelligence Methods for Financial Time Series — Giudici et al. (2024)</t>
   </si>
   <si>
@@ -419,51 +426,6 @@
   </si>
   <si>
     <t>Directly relevant because it combines LLMs, multimodal cryptocurrency data, explainable decisions and portfolio management.</t>
-  </si>
-  <si>
-    <t>Large Language Models for Cryptocurrency Transaction Analysis: A Bitcoin Case Study — Yuchen Lei, Yuexin Xiang, Qin Wang, Rafael Dowsley, Tsz Hon Yuen, Kim-Kwang Raymond Choo &amp; Jiangshan Yu (2025)</t>
-  </si>
-  <si>
-    <t>Examines whether LLMs can interpret Bitcoin transaction graphs and identify suspicious behaviour under token limits.</t>
-  </si>
-  <si>
-    <t>LLM4TG and CETraS reduced token usage; node-level accuracy exceeded 98.5%, meaningful characteristics reached 95%, and top-3 classification accuracy reached 72.43%.</t>
-  </si>
-  <si>
-    <t>Token limits, reduced temporal information, difficulty analysing large graphs and occasionally inaccurate explanations.</t>
-  </si>
-  <si>
-    <t>Relevant to explainable cryptocurrency analysis and demonstrates how LLMs can process blockchain information as an additional predictive data source.</t>
-  </si>
-  <si>
-    <t>Market-Derived Financial Sentiment Analysis: Context-Aware Language Models for Crypto Forecasting — Hamid Moradi-Kamali et al. (2025)</t>
-  </si>
-  <si>
-    <t>Replaces subjective sentiment labels with labels derived from actual Bitcoin price reactions to textual information.</t>
-  </si>
-  <si>
-    <t>Market-derived labels improved trend prediction by up to 11%; context-aware prompting achieved 89.6% accuracy and Sharpe ratios up to 5.07.</t>
-  </si>
-  <si>
-    <t>Focuses mainly on Bitcoin and short-term movements; evaluation uses a small curated news dataset and simplified backtesting assumptions.</t>
-  </si>
-  <si>
-    <t>Highly relevant because it combines LLM sentiment, market context and cryptocurrency forecasting while directly linking text to price movements.</t>
-  </si>
-  <si>
-    <t>CryptoPulse: Short-Term Cryptocurrency Forecasting with Dual-Prediction and Cross-Correlated Market Indicators — Amit Kumar &amp; Taoran Ji (2025)</t>
-  </si>
-  <si>
-    <t>Predicts next-day cryptocurrency prices using market-wide movements, technical indicators and LLM-based news sentiment.</t>
-  </si>
-  <si>
-    <t>CryptoPulse consistently outperformed ten baseline models and showed strong robustness, especially for smaller and more volatile cryptocurrencies.</t>
-  </si>
-  <si>
-    <t>Limited to next-day forecasting; sentiment may be noisy or missing, and transaction costs and live trading were not evaluated.</t>
-  </si>
-  <si>
-    <t>Directly supports combining deep learning, correlated cryptocurrencies, technical indicators and LLM sentiment in my forecasting framework.</t>
   </si>
   <si>
     <t>From Deep Learning to LLMs: A Survey of AI in Quantitative Investment — Bokai Cao, Saizhuo Wang, Xinyi Lin, Xiaojun Wu, Haohan Zhang, Lionel M. Ni &amp; Jian Guo (2025)</t>
@@ -780,13 +742,20 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
       </rPr>
       <t>Helformer: An Attention-Based Deep Learning Model for Cryptocurrency Price Forecasting</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> — T. O. Kehinde et al. (2025)</t>
     </r>
   </si>
@@ -936,34 +905,249 @@
   </si>
   <si>
     <t>Strongly supports hybrid statistical–LSTM architectures and shows that market indicators may be more reliable than sentiment alone.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cryptocurrency Forecasting Using Deep Learning Models: A Comparative Analysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Rachid Bourday, Issam Aatouchi, Mounir Ait Kerroum &amp; Ali Zaaouat (2024)</t>
+    </r>
+  </si>
+  <si>
+    <t>Compares four Transformer-based hybrid models for forecasting Bitcoin prices over 7-, 30-, and 90-day horizons using market and blockchain features.</t>
+  </si>
+  <si>
+    <t>Transformer–XGBoost achieved the best overall performance with MAE 0.011 and RMSE 0.018, outperforming Transformer–ANN, SVR and LSTM.</t>
+  </si>
+  <si>
+    <t>Limited to Bitcoin; lacks text-based sentiment analysis, XAI, independent walk-forward testing and realistic trading evaluation.</t>
+  </si>
+  <si>
+    <t>Provides a strong Transformer–XGBoost benchmark that my thesis can extend with LLM-derived sentiment, SHAP explanations and multi-cryptocurrency evaluation.</t>
+  </si>
+  <si>
+    <r>
+      <t>Crypto Currency Price Prediction through Tweets Using NLP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Arsalan Khan &amp; Imran Ihsan (2024)</t>
+    </r>
+  </si>
+  <si>
+    <t>Integrates influencer-tweet sentiment from multiple NLP models with historical cryptocurrency data for price and trend prediction.</t>
+  </si>
+  <si>
+    <t>RoBERTa achieved 91% sentiment accuracy, while Transformer obtained the lowest training and validation losses (0.0056 and 0.0773) among six forecasting models.</t>
+  </si>
+  <si>
+    <t>No complete RMSE/MAE or trading results; sentiment contribution and majority voting were not quantitatively validated, with unclear data splits and no XAI analysis.</t>
+  </si>
+  <si>
+    <t>Directly supports combining language-model sentiment with deep-learning crypto forecasting; my thesis can add ablation tests, SHAP explanations and rigorous time-series validation.</t>
+  </si>
+  <si>
+    <r>
+      <t>Integrating Moving Average Indicators with Long Short-Term Memory Model in Bitcoin Price Forecasting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Phung Duy Quang, Nguyen Hoang Duy, Pham Quang Khoai, and Bui Duc Duong (2025)</t>
+    </r>
+  </si>
+  <si>
+    <t>Improves volatile Bitcoin price forecasting by combining LSTM with SMA, EMA, and WMA across daily and hourly frequencies.</t>
+  </si>
+  <si>
+    <t>At 150 epochs, LSTM–WMA10 achieved 2.1661% MAPE on daily data, while LSTM–SMA10 achieved 0.4895% MAPE on hourly data.</t>
+  </si>
+  <si>
+    <t>Uses only Bitcoin price-based features, limited tuning, no stationarity treatment, early stopping, multiple runs, significance tests, XAI, textual data, or trading evaluation.</t>
+  </si>
+  <si>
+    <t>Provides an LSTM–technical-indicator baseline that my thesis can extend using SHAP-based explanations and LLM-derived news or sentiment features.</t>
+  </si>
+  <si>
+    <t>FinBERT-BiLSTM: A Deep Learning Model for Predicting Volatile Cryptocurrency Market Prices Using Market Sentiment Dynamics — Hossain et al. (2024)</t>
+  </si>
+  <si>
+    <t>Investigates whether financial-news sentiment can improve short- and multi-step cryptocurrency price forecasting beyond models relying only on historical prices.</t>
+  </si>
+  <si>
+    <t>FinBERT-BiLSTM produced the lowest reported errors for intra-day, one-day-ahead, and most 30-day experiments, with reported accuracy of 98.07% for BTC and 97.36% for ETH one-day-ahead forecasting; it also generated profits in the authors’ trading simulation.</t>
+  </si>
+  <si>
+    <t>Short dataset and single temporal split; potential look-ahead bias in current-day sentiment; inconsistent feature alignment between training and testing; accuracy defined as (1-\text{MAPE}); inconsistent percentage notation; no naive or buy-and-hold benchmark; limited risk metrics, statistical testing, and realistic transaction-cost modeling; data and code not openly released.</t>
+  </si>
+  <si>
+    <t>Highly relevant as a direct example of multimodal cryptocurrency forecasting using financial-language models and recurrent networks. It supports comparing price-only and sentiment-enhanced models while motivating a stronger leakage-aware framework using walk-forward validation, crypto-specific text models, SHAP, ablation analysis, and realistic financial backtesting.</t>
+  </si>
+  <si>
+    <t>Algorithm used</t>
+  </si>
+  <si>
+    <t>Methods and data</t>
+  </si>
+  <si>
+    <t>Large Language Models for Cryptocurrency Transaction Analysis: A Bitcoin Case Study — Lei et al. (2025)</t>
+  </si>
+  <si>
+    <t>Investigates whether LLMs can understand real-world Bitcoin transaction graphs, extract structural and transactional characteristics, and classify Bitcoin addresses into behavioral or illicit-activity categories while providing human-readable explanations.</t>
+  </si>
+  <si>
+    <r>
+      <t>GPT-3.5 Turbo, GPT-4 Turbo, GPT-4o, DeepSeek V3, and LLaMA 3.3-70B using few-shot prompting; LLM4TG for token-efficient textual graph representation; CETraS for connectivity-preserving graph sampling.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Traditional baselines include SVM, MLP, Decision Tree, Random Forest, CatBoost, and GNN.</t>
+    </r>
+  </si>
+  <si>
+    <t>Uses the BASD and BABD Bitcoin datasets derived from transactions between July 2019 and May 2021. BASD provides transaction subgraphs of up to 3,000 nodes, while BABD contains 148 engineered behavioral features per labeled address. The framework evaluates foundational metric extraction, graph-characteristic summarization, and eight-class address classification using either ten selected engineered features or sampled raw graphs.</t>
+  </si>
+  <si>
+    <t>Node-level information extraction generally achieved 98.50–100% accuracy, while global graph calculations achieved only 24–58%. GPT-4o produced meaningful graph characteristics in 95% of cases. DeepSeek achieved the best feature-based accuracy of 46.68% and top-3 accuracy of 72.43%, whereas GPT-4o achieved 50.49% accuracy and 63.33% precision using sampled raw graphs.</t>
+  </si>
+  <si>
+    <t>Exact classification accuracy remained moderate and generally below tree-based models and GNNs; top-3 accuracy may overstate practical performance; results depend on a small and potentially biased set of few-shot reference samples; graph compression can remove structural and temporal information; repeated-run stability, prompt sensitivity, confidence intervals, and independent explanation-faithfulness evaluations were not reported; the study covers only Bitcoin and uses data from 2019–2021.</t>
+  </si>
+  <si>
+    <t>Indirectly relevant because it demonstrates how LLMs can process structured cryptocurrency data and compares raw representations with engineered features. It supports the thesis methodology of evaluating the incremental contribution of different input types and applying explainability, but it addresses retrospective Bitcoin address classification rather than price forecasting. It also motivates testing whether price, technical indicators, news, and potentially on-chain features provide distinct predictive value and generalize across Bitcoin, Solana, and Dogecoin.</t>
+  </si>
+  <si>
+    <t>Market-Derived Financial Sentiment Analysis: Context-Aware Language Models for Crypto Forecasting — Moradi-Kamali et al. (2025)</t>
+  </si>
+  <si>
+    <t>Investigates whether Bitcoin-related tweets can predict short-term market movements more effectively when they are labeled using subsequent price behavior rather than subjective human sentiment, and whether adding market and temporal context to language-model prompts improves forecasting and trading performance.</t>
+  </si>
+  <si>
+    <t>FinBERT and CryptoBERT baselines; CryptoBERT-based Context-UnAware (CUA), Context-Aware (CA), and Temporal Context-Aware (TCA) classifiers; a Triple-Barrier-inspired market-labeling algorithm with EWMA volatility; AdamW optimization; LSTM and time-series masking autoencoder price baselines; a multi-model fusion approach; majority and mean aggregation; SHAP explainability; and vectorbt backtesting.</t>
+  </si>
+  <si>
+    <t>Uses Bitcoin tweets from 2015–2023, OHLCV data, RSI, ROC, previous-window trends, and a dataset of 227 significant Bitcoin events. Approximately 60,000 balanced tweets from 2020 are evaluated using grouped 5-fold cross-validation, while around 40,000 event-related tweets from other years form an external test dataset. Tweets are assigned Bullish, Bearish, or Neutral labels using volatility-adjusted price barriers over 8–15-day windows.</t>
+  </si>
+  <si>
+    <t>The CUA model achieved an F1-score of 43.0%, compared with 27.7% for CryptoBERT. Adding the previous trend, RSI, and ROC increased CA accuracy to 89.6% and F1 to 89.5% on the 2020 dataset, with 81.0% accuracy and 80.3% F1 on external event data. Removing the previous trend reduced accuracy to 43.6%, while removing RSI or ROC reduced it to 79.0% and 78.8%. CA-based signals were comparable or superior to LSTM, autoencoder, and fusion baselines, and the best TBL strategy achieved Sharpe ratios of 5.07, 4.70, and 3.73 in bullish, bearish, and neutral regimes.</t>
+  </si>
+  <si>
+    <t>Performance relies heavily on the previous market trend, making the independent contribution of tweets unclear. The study lacks a directly comparable market-features-only baseline and a strict walk-forward evaluation. Overlapping labeling windows, prompt-based feature construction, periodic strategy optimization, and unclear treatment of transaction costs may inflate results. SHAP evidence is mainly illustrative, cross-validation variability is high, and the study evaluates only Bitcoin and Twitter data.</t>
+  </si>
+  <si>
+    <t>Highly relevant because it directly combines textual cryptocurrency information, technical indicators, language models, explainability, and trading evaluation. It supports comparing price-only, indicator-enhanced, text-only, and multimodal models. Its limitations motivate the thesis to isolate the incremental contribution of news and individual technical features, use temporally strict validation and realistic backtesting, and test whether the framework generalizes from Bitcoin to Solana and Dogecoin.</t>
+  </si>
+  <si>
+    <t>CryptoPulse: Short-Term Cryptocurrency Forecasting with Dual-Prediction and Cross-Correlated Market Indicators — Kumar and Ji (2025)</t>
+  </si>
+  <si>
+    <t>Addresses next-day cryptocurrency closing-price forecasting by jointly modeling target-asset price dynamics, technical indicators, cross-cryptocurrency market movements, and news-derived market sentiment. It investigates whether separately forecasting from the broad crypto-market context and the target cryptocurrency’s own dynamics, followed by sentiment-guided fusion, improves short-term prediction across assets with different market capitalizations.</t>
+  </si>
+  <si>
+    <t>CryptoPulse dual-prediction architecture; 1D convolution and sinusoidal positional encoding; period-based cross-correlation attention over the five largest cryptocurrencies; a modified NLinear fluctuation predictor; GPT-3.5 Turbo with three-way few-shot think-tank prompting for positive, negative, and neutral sentiment; sentiment-guided Tanh rescaling and learned weighted fusion. Baselines include SVM, Random Forest, GRU, LSTM, Bi-LSTM, CNN-LSTM, Linear, DLinear, NLinear, and Autoformer.</t>
+  </si>
+  <si>
+    <t>Uses daily OHLCV data from Yahoo Finance for 75 cryptocurrencies from January 2021 to April 2024, seven technical indicators—Stochastic %K, Stochastic %D, Williams %R, A/D Oscillator, Momentum, Disparity 7, and ROC—and 25,210 Cointelegraph articles. A seven-day observation window predicts the next day’s closing price. Data are split chronologically into 70% training, 10% validation, and 20% testing, and results are averaged over five runs. The model creates one prediction from the top-five-cryptocurrency market context and another from the target asset’s price and technical features, then uses LLM-derived sentiment to rescale and fuse them.</t>
+  </si>
+  <si>
+    <t>CryptoPulse achieved MAEs of 0.0607 for Bitcoin, 0.0529 for Ethereum, 0.3249 for Tether, 0.0563 for Binance Coin, and 0.0511 for Solana, with reported CORR values of 0.9961, 0.9937, 0.6946, 0.9949, and 0.9962, respectively. Compared with the strongest baselines, it improved MAE by 10.4–63.8% and MSE by 17.2–69.0% for the top five assets. Across the top 10, 15, and 20 assets, MAE improvements ranged from 42.2% to 46.9%. Ablation results indicate that sentiment and technical indicators generally improve forecasting, although sentiment degraded NLinear in five of eight reported cases.</t>
+  </si>
+  <si>
+    <t>No naive last-price or random-walk baseline is reported, making it unclear whether the model materially surpasses price persistence. Price normalization and the economic units of MAE/MSE are insufficiently documented. The reported CORR formula resembles cosine similarity on price levels and may overstate predictive quality. The study does not evaluate return prediction, directional accuracy, trading performance, transaction costs, or statistical significance. GPT-3.5 sentiment labels are not validated against human annotations, prompt sensitivity is not tested, news timing and daily aggregation are unclear, and using a May 2024 market-cap threshold may introduce survivorship bias. The “macro” component contains only large cryptocurrencies rather than external macroeconomic variables, and the target asset may also appear among the five market-proxy assets.</t>
+  </si>
+  <si>
+    <t>Highly relevant because it directly integrates cryptocurrency prices, technical indicators, cross-asset information, news, an LLM, and deep forecasting across Bitcoin and Solana. It provides a strong multimodal architectural reference and supports ablation-based evaluation of different input sources. Its limitations motivate the thesis to include naive and price-only baselines, strict walk-forward validation, return and directional metrics, realistic backtesting, SHAP-based feature attribution, and explicit measurement of the incremental contribution of news, technical indicators, and cross-asset signals across Bitcoin, Solana, and Dogecoin.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -971,52 +1155,81 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1206,25 +1419,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z66"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="37.13"/>
-    <col customWidth="1" min="2" max="2" width="38.75"/>
-    <col customWidth="1" min="3" max="3" width="40.75"/>
-    <col customWidth="1" min="4" max="4" width="28.88"/>
-    <col customWidth="1" min="5" max="5" width="34.38"/>
-    <col customWidth="1" min="6" max="6" width="26.88"/>
+    <col min="1" max="1" width="37.109375" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" customWidth="1"/>
+    <col min="3" max="3" width="40.77734375" customWidth="1"/>
+    <col min="4" max="4" width="51.44140625" customWidth="1"/>
+    <col min="5" max="5" width="73.109375" customWidth="1"/>
+    <col min="6" max="6" width="57.6640625" customWidth="1"/>
+    <col min="7" max="7" width="44.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,1937 +1457,2072 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+    </row>
+    <row r="9" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+    </row>
+    <row r="11" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+    </row>
+    <row r="13" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+    </row>
+    <row r="14" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+    </row>
+    <row r="15" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+    </row>
+    <row r="16" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="3" t="s">
+    </row>
+    <row r="18" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="3" t="s">
+    </row>
+    <row r="19" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E22" s="3" t="s">
+    </row>
+    <row r="23" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="3" t="s">
+    </row>
+    <row r="24" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+    </row>
+    <row r="29" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+    </row>
+    <row r="30" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+    </row>
+    <row r="31" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+    </row>
+    <row r="32" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+    </row>
+    <row r="33" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+    </row>
+    <row r="34" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+    </row>
+    <row r="35" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+    </row>
+    <row r="36" spans="1:26" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+    </row>
+    <row r="37" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+    </row>
+    <row r="38" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+    </row>
+    <row r="39" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+    </row>
+    <row r="42" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
+    </row>
+    <row r="43" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="3"/>
+    </row>
+    <row r="44" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-      <c r="Z43" s="4"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
+    </row>
+    <row r="45" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-      <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="4"/>
-      <c r="Z44" s="4"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
+    </row>
+    <row r="46" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-      <c r="W45" s="4"/>
-      <c r="X45" s="4"/>
-      <c r="Y45" s="4"/>
-      <c r="Z45" s="4"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
+    </row>
+    <row r="47" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="4"/>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="Z46" s="4"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="3"/>
+    </row>
+    <row r="48" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-      <c r="Z47" s="4"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="3"/>
+    </row>
+    <row r="49" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
+    </row>
+    <row r="50" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
+    </row>
+    <row r="51" spans="1:26" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
+      <c r="B51" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
+    </row>
+    <row r="52" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="3"/>
+    </row>
+    <row r="53" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+    </row>
+    <row r="54" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
+    </row>
+    <row r="55" spans="1:26" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
+      <c r="B55" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
-      <c r="Z55" s="4"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+    </row>
+    <row r="58" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+    </row>
+    <row r="59" spans="1:26" s="8" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
-      <c r="Z58" s="4"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
+      <c r="B59" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E59" s="3" t="s">
+    </row>
+    <row r="60" spans="1:26" s="8" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="4"/>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
-      <c r="Z59" s="4"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
+      <c r="B60" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E60" s="3" t="s">
+    </row>
+    <row r="61" spans="1:26" s="10" customFormat="1" ht="89.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="4"/>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
-      <c r="Z60" s="4"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
+      <c r="B61" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E61" s="3" t="s">
+    </row>
+    <row r="62" spans="1:26" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
+      <c r="B62" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="1:26" ht="189" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" s="10" customFormat="1" ht="216.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="10" customFormat="1" ht="205.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A52"/>
+    <hyperlink ref="A49" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2BB1EE-D768-4AF4-8EF9-A3CB241147EA}">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="60.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>